--- a/artfynd/A 22542-2026 artfynd.xlsx
+++ b/artfynd/A 22542-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136339668</v>
       </c>
       <c r="B2" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136343166</v>
       </c>
       <c r="B3" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>136347450</v>
       </c>
       <c r="B11" t="n">
-        <v>98421</v>
+        <v>98424</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 22542-2026 artfynd.xlsx
+++ b/artfynd/A 22542-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136339668</v>
       </c>
       <c r="B2" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136343166</v>
       </c>
       <c r="B3" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>136347450</v>
       </c>
       <c r="B11" t="n">
-        <v>98424</v>
+        <v>98425</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 22542-2026 artfynd.xlsx
+++ b/artfynd/A 22542-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136339668</v>
       </c>
       <c r="B2" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136343166</v>
       </c>
       <c r="B3" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>136340969</v>
       </c>
       <c r="B8" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>136347450</v>
       </c>
       <c r="B11" t="n">
-        <v>98425</v>
+        <v>98430</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 22542-2026 artfynd.xlsx
+++ b/artfynd/A 22542-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136339668</v>
       </c>
       <c r="B2" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136343166</v>
       </c>
       <c r="B3" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>136347450</v>
       </c>
       <c r="B11" t="n">
-        <v>98430</v>
+        <v>98432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 22542-2026 artfynd.xlsx
+++ b/artfynd/A 22542-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136339668</v>
       </c>
       <c r="B2" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136343166</v>
       </c>
       <c r="B3" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>136347450</v>
       </c>
       <c r="B11" t="n">
-        <v>98432</v>
+        <v>98438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 22542-2026 artfynd.xlsx
+++ b/artfynd/A 22542-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136339668</v>
       </c>
       <c r="B2" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136343166</v>
       </c>
       <c r="B3" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>136347450</v>
       </c>
       <c r="B11" t="n">
-        <v>98438</v>
+        <v>98440</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
